--- a/catalog/data/catalog.xlsx
+++ b/catalog/data/catalog.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AM13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="27.26953125" customWidth="1" min="2" max="4"/>
@@ -572,22 +572,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Vegetables &amp; Fruits</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Rice &amp; Grains</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Egg</t>
+          <t>Dairy &amp; Eggs</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Gas Cylinder</t>
+          <t>Gas &amp; Fuel</t>
         </is>
       </c>
     </row>

--- a/catalog/data/catalog.xlsx
+++ b/catalog/data/catalog.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM13"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="27.26953125" customWidth="1" min="2" max="4"/>
@@ -1248,6 +1248,58 @@
       <c r="AK13" t="inlineStr">
         <is>
           <t>Commercial Interior</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Maid</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Baby Sitting</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>House Cleaning</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cooking</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Deep Cleaning</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Elderly Support</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Laundry &amp; Ironing</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Maternity Support</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pet Care</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Dishwashing</t>
         </is>
       </c>
     </row>
